--- a/output/pdf_financials_xlsx/KFR.xlsx
+++ b/output/pdf_financials_xlsx/KFR.xlsx
@@ -952,10 +952,10 @@
         <v>-1.5e-05</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.101091</v>
+        <v>-0.101091</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.0389</v>
+        <v>-0.0389</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.484976</v>
@@ -1128,10 +1128,10 @@
         <v>-1.5e-05</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.101091</v>
+        <v>-0.101091</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.0389</v>
+        <v>-0.0389</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.484976</v>
@@ -1236,10 +1236,10 @@
         <v>-1.5e-05</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.101091</v>
+        <v>-0.101091</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.0389</v>
+        <v>-0.0389</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.484976</v>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-3.3697</v>
+        <v>3.3697</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         <v>-1.5e-05</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.101091</v>
+        <v>-0.101091</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.0389</v>
+        <v>-0.0389</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.484976</v>
@@ -1458,10 +1458,10 @@
         <v>-1.5e-05</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.101091</v>
+        <v>-0.101091</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.0389</v>
+        <v>-0.0389</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.484976</v>
@@ -1546,10 +1546,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -16128,10 +16128,10 @@
         </is>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0.101091</v>
+        <v>-0.101091</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.0389</v>
+        <v>-0.0389</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -16983,10 +16983,10 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1.5e-05</v>
+        <v>-1.5e-05</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.101091</v>
+        <v>-0.101091</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KFR.xlsx
+++ b/output/pdf_financials_xlsx/KFR.xlsx
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.104985</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.276558</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.230644</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.116735</v>
@@ -1706,13 +1706,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.104985</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.276558</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.230644</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.116735</v>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
